--- a/apps-script/AI수업렌즈_연수응답집계.xlsx
+++ b/apps-script/AI수업렌즈_연수응답집계.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
   <si>
     <r>
       <rPr>
@@ -70,7 +70,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이 시트는 웹앱 </t>
+      <t xml:space="preserve">웹앱 </t>
     </r>
     <r>
       <rPr>
@@ -138,7 +138,58 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">을 모아 집계합니다</t>
+      <t xml:space="preserve">과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공유에 동의한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택한 이유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 모아 집계합니다</t>
     </r>
     <r>
       <rPr>
@@ -189,7 +240,41 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">선택 번호와 익명 접속 번호만 저장합니다</t>
+      <t xml:space="preserve">선택</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">익명 접속번호만 저장합니다</t>
     </r>
     <r>
       <rPr>
@@ -220,6 +305,59 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">(F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">열 숨김 말고는 직접 수정하지 않음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">집계 — 의사결정 지점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">곳의 선택별 인원과 비율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
@@ -228,7 +366,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">직접 수정하지 않음</t>
+      <t xml:space="preserve">자동 계산</t>
     </r>
     <r>
       <rPr>
@@ -241,30 +379,274 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">집계 — 의사결정 지점 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">곳의 선택별 인원과 비율 </t>
+    <t xml:space="preserve">사용 순서</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 파일을 구글 드라이브에 올리고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구글 스프레드시트로 열기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확장 프로그램 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apps Script → Code.gs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내용을 붙여넣고 저장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배포 → 새 배포 → 유형 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">웹 앱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">액세스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모든 사용자 → 배포</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나온 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">웹 앱 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">URL'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Claude</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에게 알려 주면 웹앱에 연결</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">응답 시트 열 설명</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시각 — 선택한 시각 </t>
     </r>
     <r>
       <rPr>
@@ -281,7 +663,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">자동 계산</t>
+      <t xml:space="preserve">자동</t>
     </r>
     <r>
       <rPr>
@@ -294,25 +676,111 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">사용 순서</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이 파일을 구글 드라이브에 올리고 </t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 — 도구 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">역할 중 하나</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A · B · C · D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중 하나</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">접속번호 — 브라우저마다 자동으로 만든 익명 번호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 번호가 다시 고르면 이전 선택을 덮어씀</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이유 — </t>
     </r>
     <r>
       <rPr>
@@ -329,7 +797,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구글 스프레드시트로 열기</t>
+      <t xml:space="preserve">이유도 함께 공유하기</t>
     </r>
     <r>
       <rPr>
@@ -340,228 +808,13 @@
       </rPr>
       <t xml:space="preserve">'</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확장 프로그램 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Apps Script → Code.gs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">내용을 붙여넣고 저장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배포 → 새 배포 → 유형 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">웹 앱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">' → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">액세스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모든 사용자 → 배포</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나온 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">웹 앱 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">URL'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">을 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Claude</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에게 알려 주면 웹앱에 연결</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">응답 시트 열 설명</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시각 — 선택한 시각 </t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 체크한 경우의 한 줄 이유 </t>
     </r>
     <r>
       <rPr>
@@ -578,7 +831,24 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">자동</t>
+      <t xml:space="preserve">최대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자</t>
     </r>
     <r>
       <rPr>
@@ -597,78 +867,24 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">지점 — 도구 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결과 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">역할 중 하나</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">선택 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A · B · C · D </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중 하나</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">접속번호 — 브라우저마다 자동으로 만든 익명 번호</t>
+      <t xml:space="preserve">숨김 — 강의 화면에 띄우고 싶지 않은 이유가 있으면 그 줄에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
     </r>
     <r>
       <rPr>
@@ -685,7 +901,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">같은 번호가 다시 고르면 이전 선택을 덮어씀</t>
+      <t xml:space="preserve">인원 집계에는 그대로 포함됨</t>
     </r>
   </si>
   <si>
@@ -753,7 +969,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">| B | u-k3f9a2</t>
+      <t xml:space="preserve">| B | u-k3f9a2 | </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">동의서 받는 데 시간이 걸려 시연이 현실적 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
     </r>
   </si>
   <si>
@@ -849,21 +1082,92 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노란 칸의 발표자 선택 표시만 필요하면 수정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도구 — 이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학생이 써도 될까</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">선택</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인원</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Malgun Gothic"/>
         <family val="0"/>
         <charset val="1"/>
@@ -872,6 +1176,69 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">발표자 선택</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이유 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연령 제한을 확인하고 동의서를 받은 뒤 학생이 직접 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연령 제한 확인 → 동의서 → 교사가 시연하며 제작 과정 공유</t>
+  </si>
+  <si>
+    <t xml:space="preserve">●</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학생이 쓸 수 있는 다른 도구로 바꿈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">해당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 수업에서 쓰지 않음</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">합계</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -879,7 +1246,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">도구 — 이 </t>
+      <t xml:space="preserve">결과 — </t>
     </r>
     <r>
       <rPr>
@@ -889,7 +1256,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">AI, </t>
+      <t xml:space="preserve">AI </t>
     </r>
     <r>
       <rPr>
@@ -898,7 +1265,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">학생이 써도 될까</t>
+      <t xml:space="preserve">결과</t>
     </r>
     <r>
       <rPr>
@@ -908,98 +1275,38 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">믿어도 될까</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">?</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">선택</t>
-  </si>
-  <si>
-    <t xml:space="preserve">보기</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인원</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">발표자 선택</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">연령 제한을 확인하고 동의서를 받은 뒤 학생이 직접 사용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">연령 제한 확인 → 동의서 → 교사가 시연하며 제작 과정 공유</t>
-  </si>
-  <si>
-    <t xml:space="preserve">●</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">학생이 쓸 수 있는 다른 도구로 바꿈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">해당 </t>
-    </r>
+    <t xml:space="preserve">교사가 미리 오류를 고쳐서 학생에게 제공</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오류가 있음을 먼저 안내하고 학생이 다른 자료와 대조해 직접 검증</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일단 활용하고 마지막에 한꺼번에 확인</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1015,11 +1322,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 수업에서 쓰지 않음</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">합계</t>
+      <t xml:space="preserve">가 만든 결과는 수업에 쓰지 않음</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1029,7 +1333,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">결과 — </t>
+      <t xml:space="preserve">역할 — </t>
     </r>
     <r>
       <rPr>
@@ -1048,7 +1352,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">결과</t>
+      <t xml:space="preserve">역할</t>
     </r>
     <r>
       <rPr>
@@ -1067,7 +1371,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">믿어도 될까</t>
+      <t xml:space="preserve">어디까지 맡길까</t>
     </r>
     <r>
       <rPr>
@@ -1081,15 +1385,14 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">교사가 미리 오류를 고쳐서 학생에게 제공</t>
-  </si>
-  <si>
-    <t xml:space="preserve">오류가 있음을 먼저 안내하고 학생이 다른 자료와 대조해 직접 검증</t>
-  </si>
-  <si>
-    <t xml:space="preserve">일단 활용하고 마지막에 한꺼번에 확인</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대본 전체를 </t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1105,23 +1408,14 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 만든 결과는 수업에 쓰지 않음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">역할 — </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
+      <t xml:space="preserve">에게 맡기고 학생은 다듬기만</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Malgun Gothic"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1131,50 +1425,40 @@
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">역할</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">어디까지 맡길까</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대본 전체를 </t>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">역할을 대본 수정</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">질문 보완으로 제한하고 학생이 직접 시나리오 작성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학생이 쓴 뒤 </t>
     </r>
     <r>
       <rPr>
@@ -1191,58 +1475,10 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">에게 맡기고 학생은 다듬기만</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">역할을 대본 수정</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">질문 보완으로 제한하고 학생이 직접 시나리오 작성</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">학생이 쓴 뒤 </t>
-    </r>
+      <t xml:space="preserve">가 완성도 있게 다시 써 줌</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1258,25 +1494,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 완성도 있게 다시 써 줌</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">는 쓰지 않음</t>
     </r>
   </si>
@@ -1288,6 +1505,12 @@
   </si>
   <si>
     <t xml:space="preserve">접속번호</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이유</t>
+  </si>
+  <si>
+    <t xml:space="preserve">숨김</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1699,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1571,6 +1794,10 @@
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1825,7 +2052,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1918,25 +2145,35 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>17</v>
+      <c r="A24" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1963,21 +2200,22 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1987,27 +2225,30 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="13" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"도구",응답!$C:$C,A6)</f>
@@ -2018,13 +2259,17 @@
         <v>0</v>
       </c>
       <c r="E6" s="11"/>
+      <c r="F6" s="13" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"도구",응답!$C:$C,A6,응답!$E:$E,"?*")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"도구",응답!$C:$C,A7)</f>
@@ -2035,15 +2280,19 @@
         <v>0</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"도구",응답!$C:$C,A7,응답!$E:$E,"?*")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"도구",응답!$C:$C,A8)</f>
@@ -2054,13 +2303,17 @@
         <v>0</v>
       </c>
       <c r="E8" s="11"/>
+      <c r="F8" s="13" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"도구",응답!$C:$C,A8,응답!$E:$E,"?*")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"도구",응답!$C:$C,A9)</f>
@@ -2071,10 +2324,14 @@
         <v>0</v>
       </c>
       <c r="E9" s="11"/>
+      <c r="F9" s="13" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"도구",응답!$C:$C,A9,응답!$E:$E,"?*")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" s="20" t="n">
         <f aca="false">SUM(C6:C9)</f>
@@ -2084,10 +2341,14 @@
         <f aca="false">SUM(D6:D9)</f>
         <v>0</v>
       </c>
+      <c r="F10" s="20" t="n">
+        <f aca="false">SUM(F6:F9)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2097,27 +2358,30 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C14" s="13" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"결과",응답!$C:$C,A14)</f>
@@ -2128,13 +2392,17 @@
         <v>0</v>
       </c>
       <c r="E14" s="11"/>
+      <c r="F14" s="13" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"결과",응답!$C:$C,A14,응답!$E:$E,"?*")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"결과",응답!$C:$C,A15)</f>
@@ -2145,15 +2413,19 @@
         <v>0</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"결과",응답!$C:$C,A15,응답!$E:$E,"?*")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C16" s="13" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"결과",응답!$C:$C,A16)</f>
@@ -2164,13 +2436,17 @@
         <v>0</v>
       </c>
       <c r="E16" s="11"/>
+      <c r="F16" s="13" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"결과",응답!$C:$C,A16,응답!$E:$E,"?*")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"결과",응답!$C:$C,A17)</f>
@@ -2181,10 +2457,14 @@
         <v>0</v>
       </c>
       <c r="E17" s="11"/>
+      <c r="F17" s="13" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"결과",응답!$C:$C,A17,응답!$E:$E,"?*")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C18" s="20" t="n">
         <f aca="false">SUM(C14:C17)</f>
@@ -2194,10 +2474,14 @@
         <f aca="false">SUM(D14:D17)</f>
         <v>0</v>
       </c>
+      <c r="F18" s="20" t="n">
+        <f aca="false">SUM(F14:F17)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -2207,27 +2491,30 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C22" s="13" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"역할",응답!$C:$C,A22)</f>
@@ -2238,13 +2525,17 @@
         <v>0</v>
       </c>
       <c r="E22" s="11"/>
+      <c r="F22" s="13" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"역할",응답!$C:$C,A22,응답!$E:$E,"?*")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"역할",응답!$C:$C,A23)</f>
@@ -2255,15 +2546,19 @@
         <v>0</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"역할",응답!$C:$C,A23,응답!$E:$E,"?*")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"역할",응답!$C:$C,A24)</f>
@@ -2274,13 +2569,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="11"/>
+      <c r="F24" s="13" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"역할",응답!$C:$C,A24,응답!$E:$E,"?*")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C25" s="13" t="n">
         <f aca="false">COUNTIFS(응답!$B:$B,"역할",응답!$C:$C,A25)</f>
@@ -2291,10 +2590,14 @@
         <v>0</v>
       </c>
       <c r="E25" s="11"/>
+      <c r="F25" s="13" t="n">
+        <f aca="false">COUNTIFS(응답!$B:$B,"역할",응답!$C:$C,A25,응답!$E:$E,"?*")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C26" s="20" t="n">
         <f aca="false">SUM(C22:C25)</f>
@@ -2302,6 +2605,10 @@
       </c>
       <c r="D26" s="21" t="n">
         <f aca="false">SUM(D22:D25)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <f aca="false">SUM(F22:F25)</f>
         <v>0</v>
       </c>
     </row>
@@ -2315,7 +2622,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91BF9B91-DE86-4BD9-B560-A41EE6702A79}</x14:id>
+          <x14:id>{E0361AE3-9F60-423F-B02A-3483726CDF2E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2329,7 +2636,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67456EF8-6D7B-49D4-93E8-26EBF6F03DD3}</x14:id>
+          <x14:id>{BF8B2154-545C-4B9B-9813-C038EDF56556}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2343,7 +2650,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1839F949-FD3B-4692-82D4-62E0501DCB7C}</x14:id>
+          <x14:id>{568747E4-1830-4AFD-A9D0-8239AE82B0A5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2359,7 +2666,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{91BF9B91-DE86-4BD9-B560-A41EE6702A79}">
+          <x14:cfRule type="dataBar" id="{E0361AE3-9F60-423F-B02A-3483726CDF2E}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -2374,7 +2681,7 @@
           <xm:sqref>D6:D9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{67456EF8-6D7B-49D4-93E8-26EBF6F03DD3}">
+          <x14:cfRule type="dataBar" id="{BF8B2154-545C-4B9B-9813-C038EDF56556}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -2389,7 +2696,7 @@
           <xm:sqref>D14:D17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1839F949-FD3B-4692-82D4-62E0501DCB7C}">
+          <x14:cfRule type="dataBar" id="{568747E4-1830-4AFD-A9D0-8239AE82B0A5}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -2414,27 +2721,35 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
